--- a/BWI/bestwine_output/bestwine_Bermuda.xlsx
+++ b/BWI/bestwine_output/bestwine_Bermuda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2369,6 +2369,95 @@
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Gosling's Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Gosling's Limited</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>121629</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Pembroke Parish</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>33 Front Street</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://goslingslimited.com</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>gbl@goslings.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GoslingsLimited/</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Gosling</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>President &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nancy-gosling-74332212/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
